--- a/belgeler/05_MAHAL_LISTESI.xlsx
+++ b/belgeler/05_MAHAL_LISTESI.xlsx
@@ -227,9 +227,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
@@ -281,6 +278,9 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -767,48 +767,48 @@
           <t>15.150.1005</t>
         </is>
       </c>
-      <c r="C6" s="38" t="inlineStr">
+      <c r="C6" s="37" t="inlineStr">
         <is>
           <t>C 25/30 betonarme (temel, perde, döşeme)</t>
         </is>
       </c>
-      <c r="D6" s="22" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="E6" s="22" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="F6" s="16" t="inlineStr"/>
-      <c r="G6" s="22" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="H6" s="22" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="I6" s="22" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J6" s="22" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="K6" s="22" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L6" s="16" t="inlineStr"/>
+      <c r="D6" s="21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E6" s="21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F6" s="38" t="inlineStr"/>
+      <c r="G6" s="21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="H6" s="21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I6" s="21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J6" s="21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K6" s="21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L6" s="38" t="inlineStr"/>
     </row>
     <row r="7" ht="15" customHeight="1">
       <c r="A7" s="14" t="n"/>
@@ -817,48 +817,48 @@
           <t>15.150.1003</t>
         </is>
       </c>
-      <c r="C7" s="38" t="inlineStr">
+      <c r="C7" s="37" t="inlineStr">
         <is>
           <t>C 16/20 grobeton (temel altı)</t>
         </is>
       </c>
-      <c r="D7" s="22" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="E7" s="22" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="F7" s="16" t="inlineStr"/>
-      <c r="G7" s="22" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="H7" s="22" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="I7" s="22" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J7" s="22" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="K7" s="22" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L7" s="16" t="inlineStr"/>
+      <c r="D7" s="21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E7" s="21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F7" s="38" t="inlineStr"/>
+      <c r="G7" s="21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="H7" s="21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I7" s="21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J7" s="21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K7" s="21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L7" s="38" t="inlineStr"/>
     </row>
     <row r="8" ht="15" customHeight="1">
       <c r="A8" s="14" t="n"/>
@@ -867,32 +867,32 @@
           <t>15.165.1003</t>
         </is>
       </c>
-      <c r="C8" s="38" t="inlineStr">
+      <c r="C8" s="37" t="inlineStr">
         <is>
           <t>Çelik karkas (kolon, çatı kirişi, aşık, çapraz)</t>
         </is>
       </c>
-      <c r="D8" s="22" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="E8" s="22" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="F8" s="22" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="G8" s="16" t="inlineStr"/>
-      <c r="H8" s="16" t="inlineStr"/>
-      <c r="I8" s="16" t="inlineStr"/>
-      <c r="J8" s="16" t="inlineStr"/>
-      <c r="K8" s="16" t="inlineStr"/>
-      <c r="L8" s="16" t="inlineStr"/>
+      <c r="D8" s="21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E8" s="21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F8" s="21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="G8" s="38" t="inlineStr"/>
+      <c r="H8" s="38" t="inlineStr"/>
+      <c r="I8" s="38" t="inlineStr"/>
+      <c r="J8" s="38" t="inlineStr"/>
+      <c r="K8" s="38" t="inlineStr"/>
+      <c r="L8" s="38" t="inlineStr"/>
     </row>
     <row r="9" ht="15" customHeight="1">
       <c r="A9" s="14" t="n"/>
@@ -901,48 +901,48 @@
           <t>15.160.1003</t>
         </is>
       </c>
-      <c r="C9" s="38" t="inlineStr">
+      <c r="C9" s="37" t="inlineStr">
         <is>
           <t>B420C nervürlü betonarme çeliği ø8 - ø12</t>
         </is>
       </c>
-      <c r="D9" s="22" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="E9" s="22" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="F9" s="16" t="inlineStr"/>
-      <c r="G9" s="22" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="H9" s="22" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="I9" s="22" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J9" s="22" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="K9" s="22" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L9" s="16" t="inlineStr"/>
+      <c r="D9" s="21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E9" s="21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F9" s="38" t="inlineStr"/>
+      <c r="G9" s="21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="H9" s="21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I9" s="21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J9" s="21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K9" s="21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L9" s="38" t="inlineStr"/>
     </row>
     <row r="10" ht="15" customHeight="1">
       <c r="A10" s="15" t="n"/>
@@ -951,36 +951,36 @@
           <t>15.160.1004</t>
         </is>
       </c>
-      <c r="C10" s="38" t="inlineStr">
+      <c r="C10" s="37" t="inlineStr">
         <is>
           <t>B420C nervürlü betonarme çeliği ø14 - ø28</t>
         </is>
       </c>
-      <c r="D10" s="22" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="E10" s="22" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="F10" s="16" t="inlineStr"/>
-      <c r="G10" s="22" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="H10" s="16" t="inlineStr"/>
-      <c r="I10" s="22" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J10" s="16" t="inlineStr"/>
-      <c r="K10" s="16" t="inlineStr"/>
-      <c r="L10" s="16" t="inlineStr"/>
+      <c r="D10" s="21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E10" s="21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F10" s="38" t="inlineStr"/>
+      <c r="G10" s="21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="H10" s="38" t="inlineStr"/>
+      <c r="I10" s="21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J10" s="38" t="inlineStr"/>
+      <c r="K10" s="38" t="inlineStr"/>
+      <c r="L10" s="38" t="inlineStr"/>
     </row>
     <row r="11" ht="15" customHeight="1">
       <c r="A11" s="8" t="inlineStr">
@@ -993,44 +993,44 @@
           <t>15.150.1005</t>
         </is>
       </c>
-      <c r="C11" s="38" t="inlineStr">
+      <c r="C11" s="37" t="inlineStr">
         <is>
           <t>C 25/30 betonarme zemin döşemesi (15 cm)</t>
         </is>
       </c>
-      <c r="D11" s="22" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="E11" s="22" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="F11" s="16" t="inlineStr"/>
-      <c r="G11" s="22" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="H11" s="22" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="I11" s="22" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J11" s="22" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="K11" s="16" t="inlineStr"/>
-      <c r="L11" s="16" t="inlineStr"/>
+      <c r="D11" s="21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E11" s="21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F11" s="38" t="inlineStr"/>
+      <c r="G11" s="21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="H11" s="21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I11" s="21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J11" s="21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K11" s="38" t="inlineStr"/>
+      <c r="L11" s="38" t="inlineStr"/>
     </row>
     <row r="12" ht="15" customHeight="1">
       <c r="A12" s="14" t="n"/>
@@ -1039,54 +1039,54 @@
           <t>15.160.1002</t>
         </is>
       </c>
-      <c r="C12" s="38" t="inlineStr">
+      <c r="C12" s="37" t="inlineStr">
         <is>
           <t>Q188 nervürlü çelik hasır</t>
         </is>
       </c>
-      <c r="D12" s="22" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="E12" s="22" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="F12" s="16" t="inlineStr"/>
-      <c r="G12" s="16" t="inlineStr"/>
-      <c r="H12" s="16" t="inlineStr"/>
-      <c r="I12" s="16" t="inlineStr"/>
-      <c r="J12" s="16" t="inlineStr"/>
-      <c r="K12" s="16" t="inlineStr"/>
-      <c r="L12" s="16" t="inlineStr"/>
+      <c r="D12" s="21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E12" s="21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F12" s="38" t="inlineStr"/>
+      <c r="G12" s="38" t="inlineStr"/>
+      <c r="H12" s="38" t="inlineStr"/>
+      <c r="I12" s="38" t="inlineStr"/>
+      <c r="J12" s="38" t="inlineStr"/>
+      <c r="K12" s="38" t="inlineStr"/>
+      <c r="L12" s="38" t="inlineStr"/>
     </row>
     <row r="13" ht="22" customHeight="1">
       <c r="A13" s="15" t="n"/>
-      <c r="B13" s="21" t="inlineStr">
+      <c r="B13" s="20" t="inlineStr">
         <is>
           <t>TKDK-0177</t>
         </is>
       </c>
-      <c r="C13" s="38" t="inlineStr">
+      <c r="C13" s="37" t="inlineStr">
         <is>
           <t>Duvar karosu ile döşeme kaplaması (hijyen bölmesi, ofis ve WC)</t>
         </is>
       </c>
-      <c r="D13" s="16" t="inlineStr"/>
-      <c r="E13" s="22" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="F13" s="16" t="inlineStr"/>
-      <c r="G13" s="16" t="inlineStr"/>
-      <c r="H13" s="16" t="inlineStr"/>
-      <c r="I13" s="16" t="inlineStr"/>
-      <c r="J13" s="16" t="inlineStr"/>
-      <c r="K13" s="16" t="inlineStr"/>
-      <c r="L13" s="16" t="inlineStr"/>
+      <c r="D13" s="38" t="inlineStr"/>
+      <c r="E13" s="21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F13" s="38" t="inlineStr"/>
+      <c r="G13" s="38" t="inlineStr"/>
+      <c r="H13" s="38" t="inlineStr"/>
+      <c r="I13" s="38" t="inlineStr"/>
+      <c r="J13" s="38" t="inlineStr"/>
+      <c r="K13" s="38" t="inlineStr"/>
+      <c r="L13" s="38" t="inlineStr"/>
     </row>
     <row r="14" ht="15" customHeight="1">
       <c r="A14" s="8" t="inlineStr">
@@ -1099,28 +1099,28 @@
           <t>15.225.1010</t>
         </is>
       </c>
-      <c r="C14" s="38" t="inlineStr">
+      <c r="C14" s="37" t="inlineStr">
         <is>
           <t>20 cm teçhizatsız gazbeton blok duvar (gazbeton tutkalı)</t>
         </is>
       </c>
-      <c r="D14" s="22" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="E14" s="22" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="F14" s="16" t="inlineStr"/>
-      <c r="G14" s="16" t="inlineStr"/>
-      <c r="H14" s="16" t="inlineStr"/>
-      <c r="I14" s="16" t="inlineStr"/>
-      <c r="J14" s="16" t="inlineStr"/>
-      <c r="K14" s="16" t="inlineStr"/>
-      <c r="L14" s="16" t="inlineStr"/>
+      <c r="D14" s="21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E14" s="21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F14" s="38" t="inlineStr"/>
+      <c r="G14" s="38" t="inlineStr"/>
+      <c r="H14" s="38" t="inlineStr"/>
+      <c r="I14" s="38" t="inlineStr"/>
+      <c r="J14" s="38" t="inlineStr"/>
+      <c r="K14" s="38" t="inlineStr"/>
+      <c r="L14" s="38" t="inlineStr"/>
     </row>
     <row r="15" ht="15" customHeight="1">
       <c r="A15" s="14" t="n"/>
@@ -1129,28 +1129,28 @@
           <t>15.225.1410</t>
         </is>
       </c>
-      <c r="C15" s="38" t="inlineStr">
+      <c r="C15" s="37" t="inlineStr">
         <is>
           <t>20 cm teçhizatlı gazbeton lento ve yatay hatıl</t>
         </is>
       </c>
-      <c r="D15" s="22" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="E15" s="22" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="F15" s="16" t="inlineStr"/>
-      <c r="G15" s="16" t="inlineStr"/>
-      <c r="H15" s="16" t="inlineStr"/>
-      <c r="I15" s="16" t="inlineStr"/>
-      <c r="J15" s="16" t="inlineStr"/>
-      <c r="K15" s="16" t="inlineStr"/>
-      <c r="L15" s="16" t="inlineStr"/>
+      <c r="D15" s="21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E15" s="21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F15" s="38" t="inlineStr"/>
+      <c r="G15" s="38" t="inlineStr"/>
+      <c r="H15" s="38" t="inlineStr"/>
+      <c r="I15" s="38" t="inlineStr"/>
+      <c r="J15" s="38" t="inlineStr"/>
+      <c r="K15" s="38" t="inlineStr"/>
+      <c r="L15" s="38" t="inlineStr"/>
     </row>
     <row r="16" ht="15" customHeight="1">
       <c r="A16" s="14" t="n"/>
@@ -1159,28 +1159,28 @@
           <t>15.275.1116</t>
         </is>
       </c>
-      <c r="C16" s="38" t="inlineStr">
+      <c r="C16" s="37" t="inlineStr">
         <is>
           <t>250 kg çimento dozlu kaba sıva — dış yüz</t>
         </is>
       </c>
-      <c r="D16" s="22" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="E16" s="22" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="F16" s="16" t="inlineStr"/>
-      <c r="G16" s="16" t="inlineStr"/>
-      <c r="H16" s="16" t="inlineStr"/>
-      <c r="I16" s="16" t="inlineStr"/>
-      <c r="J16" s="16" t="inlineStr"/>
-      <c r="K16" s="16" t="inlineStr"/>
-      <c r="L16" s="16" t="inlineStr"/>
+      <c r="D16" s="21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E16" s="21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F16" s="38" t="inlineStr"/>
+      <c r="G16" s="38" t="inlineStr"/>
+      <c r="H16" s="38" t="inlineStr"/>
+      <c r="I16" s="38" t="inlineStr"/>
+      <c r="J16" s="38" t="inlineStr"/>
+      <c r="K16" s="38" t="inlineStr"/>
+      <c r="L16" s="38" t="inlineStr"/>
     </row>
     <row r="17" ht="15" customHeight="1">
       <c r="A17" s="14" t="n"/>
@@ -1189,28 +1189,28 @@
           <t>15.275.1117</t>
         </is>
       </c>
-      <c r="C17" s="38" t="inlineStr">
+      <c r="C17" s="37" t="inlineStr">
         <is>
           <t>200 kg çimento ve kireç karışımı kaba sıva — iç yüz</t>
         </is>
       </c>
-      <c r="D17" s="22" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="E17" s="22" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="F17" s="16" t="inlineStr"/>
-      <c r="G17" s="16" t="inlineStr"/>
-      <c r="H17" s="16" t="inlineStr"/>
-      <c r="I17" s="16" t="inlineStr"/>
-      <c r="J17" s="16" t="inlineStr"/>
-      <c r="K17" s="16" t="inlineStr"/>
-      <c r="L17" s="16" t="inlineStr"/>
+      <c r="D17" s="21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E17" s="21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F17" s="38" t="inlineStr"/>
+      <c r="G17" s="38" t="inlineStr"/>
+      <c r="H17" s="38" t="inlineStr"/>
+      <c r="I17" s="38" t="inlineStr"/>
+      <c r="J17" s="38" t="inlineStr"/>
+      <c r="K17" s="38" t="inlineStr"/>
+      <c r="L17" s="38" t="inlineStr"/>
     </row>
     <row r="18" ht="15" customHeight="1">
       <c r="A18" s="14" t="n"/>
@@ -1219,28 +1219,28 @@
           <t>15.540.1606</t>
         </is>
       </c>
-      <c r="C18" s="38" t="inlineStr">
+      <c r="C18" s="37" t="inlineStr">
         <is>
           <t>Silikon esaslı su bazlı dış cephe boyası</t>
         </is>
       </c>
-      <c r="D18" s="22" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="E18" s="22" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="F18" s="16" t="inlineStr"/>
-      <c r="G18" s="16" t="inlineStr"/>
-      <c r="H18" s="16" t="inlineStr"/>
-      <c r="I18" s="16" t="inlineStr"/>
-      <c r="J18" s="16" t="inlineStr"/>
-      <c r="K18" s="16" t="inlineStr"/>
-      <c r="L18" s="16" t="inlineStr"/>
+      <c r="D18" s="21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E18" s="21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F18" s="38" t="inlineStr"/>
+      <c r="G18" s="38" t="inlineStr"/>
+      <c r="H18" s="38" t="inlineStr"/>
+      <c r="I18" s="38" t="inlineStr"/>
+      <c r="J18" s="38" t="inlineStr"/>
+      <c r="K18" s="38" t="inlineStr"/>
+      <c r="L18" s="38" t="inlineStr"/>
     </row>
     <row r="19" ht="15" customHeight="1">
       <c r="A19" s="14" t="n"/>
@@ -1249,28 +1249,28 @@
           <t>15.540.1537</t>
         </is>
       </c>
-      <c r="C19" s="38" t="inlineStr">
+      <c r="C19" s="37" t="inlineStr">
         <is>
           <t>Su bazlı plastik antibakteriyel iç cephe boyası</t>
         </is>
       </c>
-      <c r="D19" s="22" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="E19" s="22" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="F19" s="16" t="inlineStr"/>
-      <c r="G19" s="16" t="inlineStr"/>
-      <c r="H19" s="16" t="inlineStr"/>
-      <c r="I19" s="16" t="inlineStr"/>
-      <c r="J19" s="16" t="inlineStr"/>
-      <c r="K19" s="16" t="inlineStr"/>
-      <c r="L19" s="16" t="inlineStr"/>
+      <c r="D19" s="21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E19" s="21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F19" s="38" t="inlineStr"/>
+      <c r="G19" s="38" t="inlineStr"/>
+      <c r="H19" s="38" t="inlineStr"/>
+      <c r="I19" s="38" t="inlineStr"/>
+      <c r="J19" s="38" t="inlineStr"/>
+      <c r="K19" s="38" t="inlineStr"/>
+      <c r="L19" s="38" t="inlineStr"/>
     </row>
     <row r="20" ht="15" customHeight="1">
       <c r="A20" s="15" t="n"/>
@@ -1279,36 +1279,36 @@
           <t>15.150.1005</t>
         </is>
       </c>
-      <c r="C20" s="38" t="inlineStr">
+      <c r="C20" s="37" t="inlineStr">
         <is>
           <t>Brüt betonarme perde (kaplamasız)</t>
         </is>
       </c>
-      <c r="D20" s="16" t="inlineStr"/>
-      <c r="E20" s="16" t="inlineStr"/>
-      <c r="F20" s="16" t="inlineStr"/>
-      <c r="G20" s="22" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="H20" s="22" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="I20" s="22" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J20" s="22" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="K20" s="16" t="inlineStr"/>
-      <c r="L20" s="16" t="inlineStr"/>
+      <c r="D20" s="38" t="inlineStr"/>
+      <c r="E20" s="38" t="inlineStr"/>
+      <c r="F20" s="38" t="inlineStr"/>
+      <c r="G20" s="21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="H20" s="21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I20" s="21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J20" s="21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K20" s="38" t="inlineStr"/>
+      <c r="L20" s="38" t="inlineStr"/>
     </row>
     <row r="21" ht="15" customHeight="1">
       <c r="A21" s="8" t="inlineStr">
@@ -1316,33 +1316,33 @@
           <t>Tavan Kaplaması</t>
         </is>
       </c>
-      <c r="B21" s="21" t="inlineStr">
+      <c r="B21" s="20" t="inlineStr">
         <is>
           <t>TKDK-0042</t>
         </is>
       </c>
-      <c r="C21" s="38" t="inlineStr">
+      <c r="C21" s="37" t="inlineStr">
         <is>
           <t>6 cm poliüretan dolgulu sandviç panel (alttan görünür yüz)</t>
         </is>
       </c>
-      <c r="D21" s="22" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="E21" s="22" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="F21" s="16" t="inlineStr"/>
-      <c r="G21" s="16" t="inlineStr"/>
-      <c r="H21" s="16" t="inlineStr"/>
-      <c r="I21" s="16" t="inlineStr"/>
-      <c r="J21" s="16" t="inlineStr"/>
-      <c r="K21" s="16" t="inlineStr"/>
-      <c r="L21" s="16" t="inlineStr"/>
+      <c r="D21" s="21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E21" s="21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F21" s="38" t="inlineStr"/>
+      <c r="G21" s="38" t="inlineStr"/>
+      <c r="H21" s="38" t="inlineStr"/>
+      <c r="I21" s="38" t="inlineStr"/>
+      <c r="J21" s="38" t="inlineStr"/>
+      <c r="K21" s="38" t="inlineStr"/>
+      <c r="L21" s="38" t="inlineStr"/>
     </row>
     <row r="22" ht="15" customHeight="1">
       <c r="A22" s="15" t="n"/>
@@ -1351,36 +1351,36 @@
           <t>15.150.1005</t>
         </is>
       </c>
-      <c r="C22" s="38" t="inlineStr">
+      <c r="C22" s="37" t="inlineStr">
         <is>
           <t>C 25/30 betonarme üst döşeme</t>
         </is>
       </c>
-      <c r="D22" s="16" t="inlineStr"/>
-      <c r="E22" s="16" t="inlineStr"/>
-      <c r="F22" s="16" t="inlineStr"/>
-      <c r="G22" s="22" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="H22" s="22" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="I22" s="22" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J22" s="22" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="K22" s="16" t="inlineStr"/>
-      <c r="L22" s="16" t="inlineStr"/>
+      <c r="D22" s="38" t="inlineStr"/>
+      <c r="E22" s="38" t="inlineStr"/>
+      <c r="F22" s="38" t="inlineStr"/>
+      <c r="G22" s="21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="H22" s="21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I22" s="21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J22" s="21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K22" s="38" t="inlineStr"/>
+      <c r="L22" s="38" t="inlineStr"/>
     </row>
     <row r="23" ht="15" customHeight="1">
       <c r="A23" s="8" t="inlineStr">
@@ -1388,29 +1388,29 @@
           <t>Çatı İmalatları</t>
         </is>
       </c>
-      <c r="B23" s="21" t="inlineStr">
+      <c r="B23" s="20" t="inlineStr">
         <is>
           <t>TKDK-0042</t>
         </is>
       </c>
-      <c r="C23" s="38" t="inlineStr">
+      <c r="C23" s="37" t="inlineStr">
         <is>
           <t>6 cm poliüretan dolgulu ısı yalıtımlı sandviç çatı paneli</t>
         </is>
       </c>
-      <c r="D23" s="16" t="inlineStr"/>
-      <c r="E23" s="16" t="inlineStr"/>
-      <c r="F23" s="22" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="G23" s="16" t="inlineStr"/>
-      <c r="H23" s="16" t="inlineStr"/>
-      <c r="I23" s="16" t="inlineStr"/>
-      <c r="J23" s="16" t="inlineStr"/>
-      <c r="K23" s="16" t="inlineStr"/>
-      <c r="L23" s="16" t="inlineStr"/>
+      <c r="D23" s="38" t="inlineStr"/>
+      <c r="E23" s="38" t="inlineStr"/>
+      <c r="F23" s="21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="G23" s="38" t="inlineStr"/>
+      <c r="H23" s="38" t="inlineStr"/>
+      <c r="I23" s="38" t="inlineStr"/>
+      <c r="J23" s="38" t="inlineStr"/>
+      <c r="K23" s="38" t="inlineStr"/>
+      <c r="L23" s="38" t="inlineStr"/>
     </row>
     <row r="24" ht="15" customHeight="1">
       <c r="A24" s="14" t="n"/>
@@ -1419,50 +1419,50 @@
           <t>15.550.1202</t>
         </is>
       </c>
-      <c r="C24" s="38" t="inlineStr">
+      <c r="C24" s="37" t="inlineStr">
         <is>
           <t>Lama ve profil demirden mahya, saçak ve köşe kapaması</t>
         </is>
       </c>
-      <c r="D24" s="16" t="inlineStr"/>
-      <c r="E24" s="16" t="inlineStr"/>
-      <c r="F24" s="22" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="G24" s="16" t="inlineStr"/>
-      <c r="H24" s="16" t="inlineStr"/>
-      <c r="I24" s="16" t="inlineStr"/>
-      <c r="J24" s="16" t="inlineStr"/>
-      <c r="K24" s="16" t="inlineStr"/>
-      <c r="L24" s="16" t="inlineStr"/>
+      <c r="D24" s="38" t="inlineStr"/>
+      <c r="E24" s="38" t="inlineStr"/>
+      <c r="F24" s="21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="G24" s="38" t="inlineStr"/>
+      <c r="H24" s="38" t="inlineStr"/>
+      <c r="I24" s="38" t="inlineStr"/>
+      <c r="J24" s="38" t="inlineStr"/>
+      <c r="K24" s="38" t="inlineStr"/>
+      <c r="L24" s="38" t="inlineStr"/>
     </row>
     <row r="25" ht="15" customHeight="1">
       <c r="A25" s="15" t="n"/>
-      <c r="B25" s="21" t="inlineStr">
+      <c r="B25" s="20" t="inlineStr">
         <is>
           <t>TKDK-0115</t>
         </is>
       </c>
-      <c r="C25" s="38" t="inlineStr">
+      <c r="C25" s="37" t="inlineStr">
         <is>
           <t>Galvanizli düz sacdan yağmur oluğu ve ø100 iniş borusu</t>
         </is>
       </c>
-      <c r="D25" s="16" t="inlineStr"/>
-      <c r="E25" s="16" t="inlineStr"/>
-      <c r="F25" s="22" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="G25" s="16" t="inlineStr"/>
-      <c r="H25" s="16" t="inlineStr"/>
-      <c r="I25" s="16" t="inlineStr"/>
-      <c r="J25" s="16" t="inlineStr"/>
-      <c r="K25" s="16" t="inlineStr"/>
-      <c r="L25" s="16" t="inlineStr"/>
+      <c r="D25" s="38" t="inlineStr"/>
+      <c r="E25" s="38" t="inlineStr"/>
+      <c r="F25" s="21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="G25" s="38" t="inlineStr"/>
+      <c r="H25" s="38" t="inlineStr"/>
+      <c r="I25" s="38" t="inlineStr"/>
+      <c r="J25" s="38" t="inlineStr"/>
+      <c r="K25" s="38" t="inlineStr"/>
+      <c r="L25" s="38" t="inlineStr"/>
     </row>
     <row r="26" ht="22" customHeight="1">
       <c r="A26" s="8" t="inlineStr">
@@ -1470,55 +1470,55 @@
           <t>Kapı Doğraması</t>
         </is>
       </c>
-      <c r="B26" s="21" t="inlineStr">
+      <c r="B26" s="20" t="inlineStr">
         <is>
           <t>TKDK-0151</t>
         </is>
       </c>
-      <c r="C26" s="38" t="inlineStr">
+      <c r="C26" s="37" t="inlineStr">
         <is>
           <t>5 cm poliüretan dolgulu ısı yalıtımlı kapı — servis kapısı 100/220 ve yükleme kapısı 300/300</t>
         </is>
       </c>
-      <c r="D26" s="22" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="E26" s="16" t="inlineStr"/>
-      <c r="F26" s="16" t="inlineStr"/>
-      <c r="G26" s="16" t="inlineStr"/>
-      <c r="H26" s="16" t="inlineStr"/>
-      <c r="I26" s="16" t="inlineStr"/>
-      <c r="J26" s="16" t="inlineStr"/>
-      <c r="K26" s="16" t="inlineStr"/>
-      <c r="L26" s="16" t="inlineStr"/>
+      <c r="D26" s="21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E26" s="38" t="inlineStr"/>
+      <c r="F26" s="38" t="inlineStr"/>
+      <c r="G26" s="38" t="inlineStr"/>
+      <c r="H26" s="38" t="inlineStr"/>
+      <c r="I26" s="38" t="inlineStr"/>
+      <c r="J26" s="38" t="inlineStr"/>
+      <c r="K26" s="38" t="inlineStr"/>
+      <c r="L26" s="38" t="inlineStr"/>
     </row>
     <row r="27" ht="22" customHeight="1">
       <c r="A27" s="15" t="n"/>
-      <c r="B27" s="21" t="inlineStr">
+      <c r="B27" s="20" t="inlineStr">
         <is>
           <t>TKDK-0175</t>
         </is>
       </c>
-      <c r="C27" s="38" t="inlineStr">
+      <c r="C27" s="37" t="inlineStr">
         <is>
           <t>PVC kaplamalı MDF presli iç kapı kanadı (hijyen bölmesi, ofis ve WC)</t>
         </is>
       </c>
-      <c r="D27" s="16" t="inlineStr"/>
-      <c r="E27" s="22" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="F27" s="16" t="inlineStr"/>
-      <c r="G27" s="16" t="inlineStr"/>
-      <c r="H27" s="16" t="inlineStr"/>
-      <c r="I27" s="16" t="inlineStr"/>
-      <c r="J27" s="16" t="inlineStr"/>
-      <c r="K27" s="16" t="inlineStr"/>
-      <c r="L27" s="16" t="inlineStr"/>
+      <c r="D27" s="38" t="inlineStr"/>
+      <c r="E27" s="21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F27" s="38" t="inlineStr"/>
+      <c r="G27" s="38" t="inlineStr"/>
+      <c r="H27" s="38" t="inlineStr"/>
+      <c r="I27" s="38" t="inlineStr"/>
+      <c r="J27" s="38" t="inlineStr"/>
+      <c r="K27" s="38" t="inlineStr"/>
+      <c r="L27" s="38" t="inlineStr"/>
     </row>
     <row r="28" ht="22" customHeight="1">
       <c r="A28" s="8" t="inlineStr">
@@ -1526,32 +1526,32 @@
           <t>Çit İmalatları</t>
         </is>
       </c>
-      <c r="B28" s="21" t="inlineStr">
+      <c r="B28" s="20" t="inlineStr">
         <is>
           <t>TKDK-0091</t>
         </is>
       </c>
-      <c r="C28" s="38" t="inlineStr">
+      <c r="C28" s="37" t="inlineStr">
         <is>
           <t>Betonarme direkli galvanizli tel örgü çit (h = 1,50 m, göz 60x60 mm)</t>
         </is>
       </c>
-      <c r="D28" s="16" t="inlineStr"/>
-      <c r="E28" s="16" t="inlineStr"/>
-      <c r="F28" s="16" t="inlineStr"/>
-      <c r="G28" s="16" t="inlineStr"/>
-      <c r="H28" s="16" t="inlineStr"/>
-      <c r="I28" s="16" t="inlineStr"/>
-      <c r="J28" s="16" t="inlineStr"/>
-      <c r="K28" s="16" t="inlineStr"/>
-      <c r="L28" s="22" t="inlineStr">
+      <c r="D28" s="38" t="inlineStr"/>
+      <c r="E28" s="38" t="inlineStr"/>
+      <c r="F28" s="38" t="inlineStr"/>
+      <c r="G28" s="38" t="inlineStr"/>
+      <c r="H28" s="38" t="inlineStr"/>
+      <c r="I28" s="38" t="inlineStr"/>
+      <c r="J28" s="38" t="inlineStr"/>
+      <c r="K28" s="38" t="inlineStr"/>
+      <c r="L28" s="21" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="17" t="inlineStr">
+      <c r="A30" s="16" t="inlineStr">
         <is>
           <t>AÇIKLAMALAR</t>
         </is>
@@ -1569,35 +1569,35 @@
       <c r="L30" s="40" t="n"/>
     </row>
     <row r="31" ht="13" customHeight="1">
-      <c r="A31" s="18" t="inlineStr">
+      <c r="A31" s="17" t="inlineStr">
         <is>
           <t>•  Mahal listesi, mimari projenin ekinde sunulmak üzere hazırlanmıştır; mahal kodları mimari plandaki blok ve hacim adlarıyla eşleşir.</t>
         </is>
       </c>
     </row>
     <row r="32" ht="13" customHeight="1">
-      <c r="A32" s="18" t="inlineStr">
+      <c r="A32" s="17" t="inlineStr">
         <is>
           <t>•  Listede kullanılan poz numaraları metraj cetveli ve keşif özetiyle birebir aynıdır.</t>
         </is>
       </c>
     </row>
     <row r="33" ht="13" customHeight="1">
-      <c r="A33" s="18" t="inlineStr">
+      <c r="A33" s="17" t="inlineStr">
         <is>
           <t>•  Kümes A ve B blok birebir özdeş olduğundan tek mahal sütununda gösterilmiştir.</t>
         </is>
       </c>
     </row>
     <row r="34" ht="22" customHeight="1">
-      <c r="A34" s="18" t="inlineStr">
+      <c r="A34" s="17" t="inlineStr">
         <is>
           <t>•  Listedeki pozların tamamı birim fiyat kitaplarındandır: 15.xxx ÇŞB 2026 birim fiyat kitabı, TKDK-xxxx ise TKDK 17.02.2026 Özel Poz Tablosu pozudur.</t>
         </is>
       </c>
     </row>
     <row r="35" ht="22" customHeight="1">
-      <c r="A35" s="18" t="inlineStr">
+      <c r="A35" s="17" t="inlineStr">
         <is>
           <t>•  Gübre çukuru, ölü atma çukuru, foseptik ve depoların iç yüzeyleri kaplamasız brüt betonarmedir; su yalıtımı bu hesabın kapsamı dışında bırakılmıştır.</t>
         </is>

--- a/belgeler/05_MAHAL_LISTESI.xlsx
+++ b/belgeler/05_MAHAL_LISTESI.xlsx
@@ -186,7 +186,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="41">
+  <cellXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -280,6 +280,9 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -649,7 +652,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:L35"/>
+  <dimension ref="A1:L41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -798,17 +801,17 @@
           <t>X</t>
         </is>
       </c>
-      <c r="J6" s="21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
+      <c r="J6" s="38" t="inlineStr"/>
       <c r="K6" s="21" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="L6" s="38" t="inlineStr"/>
+      <c r="L6" s="21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="15" customHeight="1">
       <c r="A7" s="14" t="n"/>
@@ -932,17 +935,17 @@
           <t>X</t>
         </is>
       </c>
-      <c r="J9" s="21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
+      <c r="J9" s="38" t="inlineStr"/>
       <c r="K9" s="21" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="L9" s="38" t="inlineStr"/>
+      <c r="L9" s="21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
     </row>
     <row r="10" ht="15" customHeight="1">
       <c r="A10" s="15" t="n"/>
@@ -1024,11 +1027,7 @@
           <t>X</t>
         </is>
       </c>
-      <c r="J11" s="21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
+      <c r="J11" s="38" t="inlineStr"/>
       <c r="K11" s="38" t="inlineStr"/>
       <c r="L11" s="38" t="inlineStr"/>
     </row>
@@ -1152,23 +1151,19 @@
       <c r="K15" s="38" t="inlineStr"/>
       <c r="L15" s="38" t="inlineStr"/>
     </row>
-    <row r="16" ht="15" customHeight="1">
+    <row r="16" ht="22" customHeight="1">
       <c r="A16" s="14" t="n"/>
       <c r="B16" s="10" t="inlineStr">
         <is>
-          <t>15.275.1116</t>
+          <t>15.225.1004</t>
         </is>
       </c>
       <c r="C16" s="37" t="inlineStr">
         <is>
-          <t>250 kg çimento dozlu kaba sıva — dış yüz</t>
-        </is>
-      </c>
-      <c r="D16" s="21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
+          <t>10 cm teçhizatsız gazbeton blok bölme duvarı (servis bölümü)</t>
+        </is>
+      </c>
+      <c r="D16" s="38" t="inlineStr"/>
       <c r="E16" s="21" t="inlineStr">
         <is>
           <t>X</t>
@@ -1186,12 +1181,12 @@
       <c r="A17" s="14" t="n"/>
       <c r="B17" s="10" t="inlineStr">
         <is>
-          <t>15.275.1117</t>
+          <t>15.275.1116</t>
         </is>
       </c>
       <c r="C17" s="37" t="inlineStr">
         <is>
-          <t>200 kg çimento ve kireç karışımı kaba sıva — iç yüz</t>
+          <t>250 kg çimento dozlu kaba sıva — dış yüz</t>
         </is>
       </c>
       <c r="D17" s="21" t="inlineStr">
@@ -1216,12 +1211,12 @@
       <c r="A18" s="14" t="n"/>
       <c r="B18" s="10" t="inlineStr">
         <is>
-          <t>15.540.1606</t>
+          <t>15.275.1117</t>
         </is>
       </c>
       <c r="C18" s="37" t="inlineStr">
         <is>
-          <t>Silikon esaslı su bazlı dış cephe boyası</t>
+          <t>200 kg çimento ve kireç karışımı kaba sıva — iç yüz</t>
         </is>
       </c>
       <c r="D18" s="21" t="inlineStr">
@@ -1246,12 +1241,12 @@
       <c r="A19" s="14" t="n"/>
       <c r="B19" s="10" t="inlineStr">
         <is>
-          <t>15.540.1537</t>
+          <t>15.540.1606</t>
         </is>
       </c>
       <c r="C19" s="37" t="inlineStr">
         <is>
-          <t>Su bazlı plastik antibakteriyel iç cephe boyası</t>
+          <t>Silikon esaslı su bazlı dış cephe boyası</t>
         </is>
       </c>
       <c r="D19" s="21" t="inlineStr">
@@ -1273,155 +1268,151 @@
       <c r="L19" s="38" t="inlineStr"/>
     </row>
     <row r="20" ht="15" customHeight="1">
-      <c r="A20" s="15" t="n"/>
+      <c r="A20" s="14" t="n"/>
       <c r="B20" s="10" t="inlineStr">
         <is>
-          <t>15.150.1005</t>
+          <t>15.540.1537</t>
         </is>
       </c>
       <c r="C20" s="37" t="inlineStr">
         <is>
-          <t>Brüt betonarme perde (kaplamasız)</t>
-        </is>
-      </c>
-      <c r="D20" s="38" t="inlineStr"/>
-      <c r="E20" s="38" t="inlineStr"/>
+          <t>Su bazlı plastik antibakteriyel iç cephe boyası</t>
+        </is>
+      </c>
+      <c r="D20" s="21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E20" s="21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="F20" s="38" t="inlineStr"/>
-      <c r="G20" s="21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="H20" s="21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="I20" s="21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J20" s="21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
+      <c r="G20" s="38" t="inlineStr"/>
+      <c r="H20" s="38" t="inlineStr"/>
+      <c r="I20" s="38" t="inlineStr"/>
+      <c r="J20" s="38" t="inlineStr"/>
       <c r="K20" s="38" t="inlineStr"/>
       <c r="L20" s="38" t="inlineStr"/>
     </row>
     <row r="21" ht="15" customHeight="1">
-      <c r="A21" s="8" t="inlineStr">
-        <is>
-          <t>Tavan Kaplaması</t>
-        </is>
-      </c>
-      <c r="B21" s="20" t="inlineStr">
-        <is>
-          <t>TKDK-0042</t>
+      <c r="A21" s="15" t="n"/>
+      <c r="B21" s="10" t="inlineStr">
+        <is>
+          <t>15.150.1005</t>
         </is>
       </c>
       <c r="C21" s="37" t="inlineStr">
         <is>
-          <t>6 cm poliüretan dolgulu sandviç panel (alttan görünür yüz)</t>
-        </is>
-      </c>
-      <c r="D21" s="21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="E21" s="21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
+          <t>Brüt betonarme perde (kaplamasız)</t>
+        </is>
+      </c>
+      <c r="D21" s="38" t="inlineStr"/>
+      <c r="E21" s="38" t="inlineStr"/>
       <c r="F21" s="38" t="inlineStr"/>
-      <c r="G21" s="38" t="inlineStr"/>
-      <c r="H21" s="38" t="inlineStr"/>
-      <c r="I21" s="38" t="inlineStr"/>
+      <c r="G21" s="21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="H21" s="21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I21" s="21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J21" s="38" t="inlineStr"/>
       <c r="K21" s="38" t="inlineStr"/>
       <c r="L21" s="38" t="inlineStr"/>
     </row>
     <row r="22" ht="15" customHeight="1">
-      <c r="A22" s="15" t="n"/>
-      <c r="B22" s="10" t="inlineStr">
-        <is>
-          <t>15.150.1005</t>
+      <c r="A22" s="8" t="inlineStr">
+        <is>
+          <t>Tavan Kaplaması</t>
+        </is>
+      </c>
+      <c r="B22" s="20" t="inlineStr">
+        <is>
+          <t>TKDK-0042</t>
         </is>
       </c>
       <c r="C22" s="37" t="inlineStr">
         <is>
-          <t>C 25/30 betonarme üst döşeme</t>
-        </is>
-      </c>
-      <c r="D22" s="38" t="inlineStr"/>
-      <c r="E22" s="38" t="inlineStr"/>
+          <t>6 cm poliüretan dolgulu sandviç panel (alttan görünür yüz)</t>
+        </is>
+      </c>
+      <c r="D22" s="21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E22" s="21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="F22" s="38" t="inlineStr"/>
-      <c r="G22" s="21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="H22" s="21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="I22" s="21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J22" s="21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
+      <c r="G22" s="38" t="inlineStr"/>
+      <c r="H22" s="38" t="inlineStr"/>
+      <c r="I22" s="38" t="inlineStr"/>
+      <c r="J22" s="38" t="inlineStr"/>
       <c r="K22" s="38" t="inlineStr"/>
       <c r="L22" s="38" t="inlineStr"/>
     </row>
     <row r="23" ht="15" customHeight="1">
-      <c r="A23" s="8" t="inlineStr">
-        <is>
-          <t>Çatı İmalatları</t>
-        </is>
-      </c>
-      <c r="B23" s="20" t="inlineStr">
-        <is>
-          <t>TKDK-0042</t>
+      <c r="A23" s="15" t="n"/>
+      <c r="B23" s="10" t="inlineStr">
+        <is>
+          <t>15.150.1005</t>
         </is>
       </c>
       <c r="C23" s="37" t="inlineStr">
         <is>
-          <t>6 cm poliüretan dolgulu ısı yalıtımlı sandviç çatı paneli</t>
+          <t>C 25/30 betonarme üst döşeme</t>
         </is>
       </c>
       <c r="D23" s="38" t="inlineStr"/>
       <c r="E23" s="38" t="inlineStr"/>
-      <c r="F23" s="21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="G23" s="38" t="inlineStr"/>
-      <c r="H23" s="38" t="inlineStr"/>
-      <c r="I23" s="38" t="inlineStr"/>
+      <c r="F23" s="38" t="inlineStr"/>
+      <c r="G23" s="21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="H23" s="21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I23" s="21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="J23" s="38" t="inlineStr"/>
       <c r="K23" s="38" t="inlineStr"/>
       <c r="L23" s="38" t="inlineStr"/>
     </row>
     <row r="24" ht="15" customHeight="1">
-      <c r="A24" s="14" t="n"/>
-      <c r="B24" s="10" t="inlineStr">
-        <is>
-          <t>15.550.1202</t>
+      <c r="A24" s="8" t="inlineStr">
+        <is>
+          <t>Çatı İmalatları</t>
+        </is>
+      </c>
+      <c r="B24" s="20" t="inlineStr">
+        <is>
+          <t>TKDK-0042</t>
         </is>
       </c>
       <c r="C24" s="37" t="inlineStr">
         <is>
-          <t>Lama ve profil demirden mahya, saçak ve köşe kapaması</t>
+          <t>6 cm poliüretan dolgulu ısı yalıtımlı sandviç çatı paneli</t>
         </is>
       </c>
       <c r="D24" s="38" t="inlineStr"/>
@@ -1439,15 +1430,15 @@
       <c r="L24" s="38" t="inlineStr"/>
     </row>
     <row r="25" ht="15" customHeight="1">
-      <c r="A25" s="15" t="n"/>
-      <c r="B25" s="20" t="inlineStr">
-        <is>
-          <t>TKDK-0115</t>
+      <c r="A25" s="14" t="n"/>
+      <c r="B25" s="10" t="inlineStr">
+        <is>
+          <t>15.550.1202</t>
         </is>
       </c>
       <c r="C25" s="37" t="inlineStr">
         <is>
-          <t>Galvanizli düz sacdan yağmur oluğu ve ø100 iniş borusu</t>
+          <t>Lama ve profil demirden mahya, saçak ve köşe kapaması</t>
         </is>
       </c>
       <c r="D25" s="38" t="inlineStr"/>
@@ -1464,29 +1455,25 @@
       <c r="K25" s="38" t="inlineStr"/>
       <c r="L25" s="38" t="inlineStr"/>
     </row>
-    <row r="26" ht="22" customHeight="1">
-      <c r="A26" s="8" t="inlineStr">
-        <is>
-          <t>Kapı Doğraması</t>
-        </is>
-      </c>
+    <row r="26" ht="15" customHeight="1">
+      <c r="A26" s="14" t="n"/>
       <c r="B26" s="20" t="inlineStr">
         <is>
-          <t>TKDK-0151</t>
+          <t>TKDK-0115</t>
         </is>
       </c>
       <c r="C26" s="37" t="inlineStr">
         <is>
-          <t>5 cm poliüretan dolgulu ısı yalıtımlı kapı — servis kapısı 100/220 ve yükleme kapısı 300/300</t>
-        </is>
-      </c>
-      <c r="D26" s="21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
+          <t>Galvanizli düz sacdan yağmur oluğu (dere)</t>
+        </is>
+      </c>
+      <c r="D26" s="38" t="inlineStr"/>
       <c r="E26" s="38" t="inlineStr"/>
-      <c r="F26" s="38" t="inlineStr"/>
+      <c r="F26" s="21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="G26" s="38" t="inlineStr"/>
       <c r="H26" s="38" t="inlineStr"/>
       <c r="I26" s="38" t="inlineStr"/>
@@ -1494,25 +1481,25 @@
       <c r="K26" s="38" t="inlineStr"/>
       <c r="L26" s="38" t="inlineStr"/>
     </row>
-    <row r="27" ht="22" customHeight="1">
+    <row r="27" ht="15" customHeight="1">
       <c r="A27" s="15" t="n"/>
-      <c r="B27" s="20" t="inlineStr">
-        <is>
-          <t>TKDK-0175</t>
+      <c r="B27" s="10" t="inlineStr">
+        <is>
+          <t>15.315.1001</t>
         </is>
       </c>
       <c r="C27" s="37" t="inlineStr">
         <is>
-          <t>PVC kaplamalı MDF presli iç kapı kanadı (hijyen bölmesi, ofis ve WC)</t>
+          <t>Ø70 sert PVC yağmur suyu iniş borusu</t>
         </is>
       </c>
       <c r="D27" s="38" t="inlineStr"/>
-      <c r="E27" s="21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="F27" s="38" t="inlineStr"/>
+      <c r="E27" s="38" t="inlineStr"/>
+      <c r="F27" s="21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="G27" s="38" t="inlineStr"/>
       <c r="H27" s="38" t="inlineStr"/>
       <c r="I27" s="38" t="inlineStr"/>
@@ -1523,20 +1510,24 @@
     <row r="28" ht="22" customHeight="1">
       <c r="A28" s="8" t="inlineStr">
         <is>
-          <t>Çit İmalatları</t>
+          <t>Kapı Doğraması</t>
         </is>
       </c>
       <c r="B28" s="20" t="inlineStr">
         <is>
-          <t>TKDK-0091</t>
+          <t>TKDK-0151</t>
         </is>
       </c>
       <c r="C28" s="37" t="inlineStr">
         <is>
-          <t>Betonarme direkli galvanizli tel örgü çit (h = 1,50 m, göz 60x60 mm)</t>
-        </is>
-      </c>
-      <c r="D28" s="38" t="inlineStr"/>
+          <t>5 cm poliüretan dolgulu ısı yalıtımlı kapı — servis kapısı 100/220 ve yükleme kapısı 300/300</t>
+        </is>
+      </c>
+      <c r="D28" s="21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="E28" s="38" t="inlineStr"/>
       <c r="F28" s="38" t="inlineStr"/>
       <c r="G28" s="38" t="inlineStr"/>
@@ -1544,81 +1535,246 @@
       <c r="I28" s="38" t="inlineStr"/>
       <c r="J28" s="38" t="inlineStr"/>
       <c r="K28" s="38" t="inlineStr"/>
-      <c r="L28" s="21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="16" t="inlineStr">
+      <c r="L28" s="38" t="inlineStr"/>
+    </row>
+    <row r="29" ht="22" customHeight="1">
+      <c r="A29" s="14" t="n"/>
+      <c r="B29" s="20" t="inlineStr">
+        <is>
+          <t>TKDK-0175</t>
+        </is>
+      </c>
+      <c r="C29" s="37" t="inlineStr">
+        <is>
+          <t>PVC kaplamalı MDF presli iç kapı kanadı (hijyen bölmesi, ofis ve WC)</t>
+        </is>
+      </c>
+      <c r="D29" s="38" t="inlineStr"/>
+      <c r="E29" s="21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F29" s="38" t="inlineStr"/>
+      <c r="G29" s="38" t="inlineStr"/>
+      <c r="H29" s="38" t="inlineStr"/>
+      <c r="I29" s="38" t="inlineStr"/>
+      <c r="J29" s="38" t="inlineStr"/>
+      <c r="K29" s="38" t="inlineStr"/>
+      <c r="L29" s="38" t="inlineStr"/>
+    </row>
+    <row r="30" ht="22" customHeight="1">
+      <c r="A30" s="15" t="n"/>
+      <c r="B30" s="10" t="inlineStr">
+        <is>
+          <t>15.550.1002</t>
+        </is>
+      </c>
+      <c r="C30" s="37" t="inlineStr">
+        <is>
+          <t>1,50 mm sacdan bükme kapı kasası (hijyen bölmesi, ofis ve WC)</t>
+        </is>
+      </c>
+      <c r="D30" s="38" t="inlineStr"/>
+      <c r="E30" s="21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F30" s="38" t="inlineStr"/>
+      <c r="G30" s="38" t="inlineStr"/>
+      <c r="H30" s="38" t="inlineStr"/>
+      <c r="I30" s="38" t="inlineStr"/>
+      <c r="J30" s="38" t="inlineStr"/>
+      <c r="K30" s="38" t="inlineStr"/>
+      <c r="L30" s="38" t="inlineStr"/>
+    </row>
+    <row r="31" ht="15" customHeight="1">
+      <c r="A31" s="8" t="inlineStr">
+        <is>
+          <t>Kanalizasyon İmalatları</t>
+        </is>
+      </c>
+      <c r="B31" s="39" t="inlineStr">
+        <is>
+          <t>ÖP-15</t>
+        </is>
+      </c>
+      <c r="C31" s="37" t="inlineStr">
+        <is>
+          <t>Prefabrik polietilen sızdırmaz foseptik tankı — 6 m³</t>
+        </is>
+      </c>
+      <c r="D31" s="38" t="inlineStr"/>
+      <c r="E31" s="38" t="inlineStr"/>
+      <c r="F31" s="38" t="inlineStr"/>
+      <c r="G31" s="38" t="inlineStr"/>
+      <c r="H31" s="38" t="inlineStr"/>
+      <c r="I31" s="38" t="inlineStr"/>
+      <c r="J31" s="21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K31" s="38" t="inlineStr"/>
+      <c r="L31" s="38" t="inlineStr"/>
+    </row>
+    <row r="32" ht="15" customHeight="1">
+      <c r="A32" s="14" t="n"/>
+      <c r="B32" s="10" t="inlineStr">
+        <is>
+          <t>43.527.1001</t>
+        </is>
+      </c>
+      <c r="C32" s="37" t="inlineStr">
+        <is>
+          <t>Ø150 HDPE koruge pissu borusu (SN 8)</t>
+        </is>
+      </c>
+      <c r="D32" s="38" t="inlineStr"/>
+      <c r="E32" s="21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F32" s="38" t="inlineStr"/>
+      <c r="G32" s="38" t="inlineStr"/>
+      <c r="H32" s="38" t="inlineStr"/>
+      <c r="I32" s="38" t="inlineStr"/>
+      <c r="J32" s="38" t="inlineStr"/>
+      <c r="K32" s="38" t="inlineStr"/>
+      <c r="L32" s="21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="15" customHeight="1">
+      <c r="A33" s="15" t="n"/>
+      <c r="B33" s="10" t="inlineStr">
+        <is>
+          <t>15.560.1003</t>
+        </is>
+      </c>
+      <c r="C33" s="37" t="inlineStr">
+        <is>
+          <t>Betonarme kompozit rögar kapağı</t>
+        </is>
+      </c>
+      <c r="D33" s="38" t="inlineStr"/>
+      <c r="E33" s="38" t="inlineStr"/>
+      <c r="F33" s="38" t="inlineStr"/>
+      <c r="G33" s="38" t="inlineStr"/>
+      <c r="H33" s="38" t="inlineStr"/>
+      <c r="I33" s="38" t="inlineStr"/>
+      <c r="J33" s="38" t="inlineStr"/>
+      <c r="K33" s="38" t="inlineStr"/>
+      <c r="L33" s="21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="22" customHeight="1">
+      <c r="A34" s="8" t="inlineStr">
+        <is>
+          <t>Çit İmalatları</t>
+        </is>
+      </c>
+      <c r="B34" s="20" t="inlineStr">
+        <is>
+          <t>TKDK-0091</t>
+        </is>
+      </c>
+      <c r="C34" s="37" t="inlineStr">
+        <is>
+          <t>Betonarme direkli galvanizli tel örgü çit (h = 1,50 m, göz 60x60 mm)</t>
+        </is>
+      </c>
+      <c r="D34" s="38" t="inlineStr"/>
+      <c r="E34" s="38" t="inlineStr"/>
+      <c r="F34" s="38" t="inlineStr"/>
+      <c r="G34" s="38" t="inlineStr"/>
+      <c r="H34" s="38" t="inlineStr"/>
+      <c r="I34" s="38" t="inlineStr"/>
+      <c r="J34" s="38" t="inlineStr"/>
+      <c r="K34" s="38" t="inlineStr"/>
+      <c r="L34" s="21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="16" t="inlineStr">
         <is>
           <t>AÇIKLAMALAR</t>
         </is>
       </c>
-      <c r="B30" s="39" t="n"/>
-      <c r="C30" s="39" t="n"/>
-      <c r="D30" s="39" t="n"/>
-      <c r="E30" s="39" t="n"/>
-      <c r="F30" s="39" t="n"/>
-      <c r="G30" s="39" t="n"/>
-      <c r="H30" s="39" t="n"/>
-      <c r="I30" s="39" t="n"/>
-      <c r="J30" s="39" t="n"/>
-      <c r="K30" s="39" t="n"/>
-      <c r="L30" s="40" t="n"/>
-    </row>
-    <row r="31" ht="13" customHeight="1">
-      <c r="A31" s="17" t="inlineStr">
+      <c r="B36" s="40" t="n"/>
+      <c r="C36" s="40" t="n"/>
+      <c r="D36" s="40" t="n"/>
+      <c r="E36" s="40" t="n"/>
+      <c r="F36" s="40" t="n"/>
+      <c r="G36" s="40" t="n"/>
+      <c r="H36" s="40" t="n"/>
+      <c r="I36" s="40" t="n"/>
+      <c r="J36" s="40" t="n"/>
+      <c r="K36" s="40" t="n"/>
+      <c r="L36" s="41" t="n"/>
+    </row>
+    <row r="37" ht="13" customHeight="1">
+      <c r="A37" s="17" t="inlineStr">
         <is>
           <t>•  Mahal listesi, mimari projenin ekinde sunulmak üzere hazırlanmıştır; mahal kodları mimari plandaki blok ve hacim adlarıyla eşleşir.</t>
         </is>
       </c>
     </row>
-    <row r="32" ht="13" customHeight="1">
-      <c r="A32" s="17" t="inlineStr">
+    <row r="38" ht="13" customHeight="1">
+      <c r="A38" s="17" t="inlineStr">
         <is>
           <t>•  Listede kullanılan poz numaraları metraj cetveli ve keşif özetiyle birebir aynıdır.</t>
         </is>
       </c>
     </row>
-    <row r="33" ht="13" customHeight="1">
-      <c r="A33" s="17" t="inlineStr">
+    <row r="39" ht="13" customHeight="1">
+      <c r="A39" s="17" t="inlineStr">
         <is>
           <t>•  Kümes A ve B blok birebir özdeş olduğundan tek mahal sütununda gösterilmiştir.</t>
         </is>
       </c>
     </row>
-    <row r="34" ht="22" customHeight="1">
-      <c r="A34" s="17" t="inlineStr">
+    <row r="40" ht="22" customHeight="1">
+      <c r="A40" s="17" t="inlineStr">
         <is>
           <t>•  Listedeki pozların tamamı birim fiyat kitaplarındandır: 15.xxx ÇŞB 2026 birim fiyat kitabı, TKDK-xxxx ise TKDK 17.02.2026 Özel Poz Tablosu pozudur.</t>
         </is>
       </c>
     </row>
-    <row r="35" ht="22" customHeight="1">
-      <c r="A35" s="17" t="inlineStr">
-        <is>
-          <t>•  Gübre çukuru, ölü atma çukuru, foseptik ve depoların iç yüzeyleri kaplamasız brüt betonarmedir; su yalıtımı bu hesabın kapsamı dışında bırakılmıştır.</t>
+    <row r="41" ht="22" customHeight="1">
+      <c r="A41" s="17" t="inlineStr">
+        <is>
+          <t>•  Gübre çukuru, ölü atma çukuru ve depoların iç yüzeyleri kaplamasız brüt betonarmedir; su yalıtımı bu hesabın kapsamı dışında bırakılmıştır. Foseptik betonarme değildir: kazı ve grobeton oturma yatağı üzerine yerleştirilen prefabrik polietilen sızdırmaz tanktır.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="15">
-    <mergeCell ref="A30:L30"/>
+  <mergeCells count="16">
+    <mergeCell ref="A38:L38"/>
     <mergeCell ref="A2:L2"/>
-    <mergeCell ref="A33:L33"/>
-    <mergeCell ref="A26:A27"/>
+    <mergeCell ref="A22:A23"/>
+    <mergeCell ref="A41:L41"/>
+    <mergeCell ref="A24:A27"/>
     <mergeCell ref="A1:L1"/>
-    <mergeCell ref="A32:L32"/>
+    <mergeCell ref="A28:A30"/>
+    <mergeCell ref="A37:L37"/>
+    <mergeCell ref="A36:L36"/>
     <mergeCell ref="A11:A13"/>
-    <mergeCell ref="A31:L31"/>
-    <mergeCell ref="A14:A20"/>
-    <mergeCell ref="A23:A25"/>
+    <mergeCell ref="A40:L40"/>
+    <mergeCell ref="A14:A21"/>
+    <mergeCell ref="A31:A33"/>
     <mergeCell ref="A3:L3"/>
-    <mergeCell ref="A34:L34"/>
-    <mergeCell ref="A35:L35"/>
-    <mergeCell ref="A21:A22"/>
+    <mergeCell ref="A39:L39"/>
     <mergeCell ref="A6:A10"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/belgeler/05_MAHAL_LISTESI.xlsx
+++ b/belgeler/05_MAHAL_LISTESI.xlsx
@@ -652,7 +652,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:L41"/>
+  <dimension ref="A1:L48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -1705,76 +1705,249 @@
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="16" t="inlineStr">
+    <row r="35" ht="22" customHeight="1">
+      <c r="A35" s="8" t="inlineStr">
+        <is>
+          <t>Sıhhi Tesisat</t>
+        </is>
+      </c>
+      <c r="B35" s="38" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C35" s="37" t="inlineStr">
+        <is>
+          <t>Temiz su tesisatı — PPRC boru ve ek parçaları, küresel vanalar, askı ve kılıflar</t>
+        </is>
+      </c>
+      <c r="D35" s="21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E35" s="21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F35" s="38" t="inlineStr"/>
+      <c r="G35" s="38" t="inlineStr"/>
+      <c r="H35" s="38" t="inlineStr"/>
+      <c r="I35" s="38" t="inlineStr"/>
+      <c r="J35" s="38" t="inlineStr"/>
+      <c r="K35" s="38" t="inlineStr"/>
+      <c r="L35" s="38" t="inlineStr"/>
+    </row>
+    <row r="36" ht="22" customHeight="1">
+      <c r="A36" s="14" t="n"/>
+      <c r="B36" s="38" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C36" s="37" t="inlineStr">
+        <is>
+          <t>Pis su tesisatı — Ø50 / Ø70 / Ø100 sert PVC boru, temizleme kapağı, yer süzgeci</t>
+        </is>
+      </c>
+      <c r="D36" s="38" t="inlineStr"/>
+      <c r="E36" s="21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F36" s="38" t="inlineStr"/>
+      <c r="G36" s="38" t="inlineStr"/>
+      <c r="H36" s="38" t="inlineStr"/>
+      <c r="I36" s="38" t="inlineStr"/>
+      <c r="J36" s="38" t="inlineStr"/>
+      <c r="K36" s="38" t="inlineStr"/>
+      <c r="L36" s="38" t="inlineStr"/>
+    </row>
+    <row r="37" ht="15" customHeight="1">
+      <c r="A37" s="14" t="n"/>
+      <c r="B37" s="38" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C37" s="37" t="inlineStr">
+        <is>
+          <t>Termosifon — sıcak su üretimi</t>
+        </is>
+      </c>
+      <c r="D37" s="38" t="inlineStr"/>
+      <c r="E37" s="21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F37" s="38" t="inlineStr"/>
+      <c r="G37" s="38" t="inlineStr"/>
+      <c r="H37" s="38" t="inlineStr"/>
+      <c r="I37" s="38" t="inlineStr"/>
+      <c r="J37" s="38" t="inlineStr"/>
+      <c r="K37" s="38" t="inlineStr"/>
+      <c r="L37" s="38" t="inlineStr"/>
+    </row>
+    <row r="38" ht="15" customHeight="1">
+      <c r="A38" s="14" t="n"/>
+      <c r="B38" s="38" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C38" s="37" t="inlineStr">
+        <is>
+          <t>Şebeke su bağlantısı ve 2" su sayacı</t>
+        </is>
+      </c>
+      <c r="D38" s="38" t="inlineStr"/>
+      <c r="E38" s="38" t="inlineStr"/>
+      <c r="F38" s="38" t="inlineStr"/>
+      <c r="G38" s="38" t="inlineStr"/>
+      <c r="H38" s="38" t="inlineStr"/>
+      <c r="I38" s="38" t="inlineStr"/>
+      <c r="J38" s="38" t="inlineStr"/>
+      <c r="K38" s="38" t="inlineStr"/>
+      <c r="L38" s="21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="15" customHeight="1">
+      <c r="A39" s="14" t="n"/>
+      <c r="B39" s="38" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C39" s="37" t="inlineStr">
+        <is>
+          <t>Hidrofor — Q = 2 m³/h, P = 33-38 mSS</t>
+        </is>
+      </c>
+      <c r="D39" s="38" t="inlineStr"/>
+      <c r="E39" s="38" t="inlineStr"/>
+      <c r="F39" s="38" t="inlineStr"/>
+      <c r="G39" s="38" t="inlineStr"/>
+      <c r="H39" s="38" t="inlineStr"/>
+      <c r="I39" s="38" t="inlineStr"/>
+      <c r="J39" s="38" t="inlineStr"/>
+      <c r="K39" s="38" t="inlineStr"/>
+      <c r="L39" s="21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="15" customHeight="1">
+      <c r="A40" s="15" t="n"/>
+      <c r="B40" s="38" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C40" s="37" t="inlineStr">
+        <is>
+          <t>Tesisat hidroforu — 0,3 m³/h, 30 mSS</t>
+        </is>
+      </c>
+      <c r="D40" s="38" t="inlineStr"/>
+      <c r="E40" s="38" t="inlineStr"/>
+      <c r="F40" s="38" t="inlineStr"/>
+      <c r="G40" s="38" t="inlineStr"/>
+      <c r="H40" s="38" t="inlineStr"/>
+      <c r="I40" s="38" t="inlineStr"/>
+      <c r="J40" s="38" t="inlineStr"/>
+      <c r="K40" s="38" t="inlineStr"/>
+      <c r="L40" s="21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="16" t="inlineStr">
         <is>
           <t>AÇIKLAMALAR</t>
         </is>
       </c>
-      <c r="B36" s="40" t="n"/>
-      <c r="C36" s="40" t="n"/>
-      <c r="D36" s="40" t="n"/>
-      <c r="E36" s="40" t="n"/>
-      <c r="F36" s="40" t="n"/>
-      <c r="G36" s="40" t="n"/>
-      <c r="H36" s="40" t="n"/>
-      <c r="I36" s="40" t="n"/>
-      <c r="J36" s="40" t="n"/>
-      <c r="K36" s="40" t="n"/>
-      <c r="L36" s="41" t="n"/>
-    </row>
-    <row r="37" ht="13" customHeight="1">
-      <c r="A37" s="17" t="inlineStr">
+      <c r="B42" s="40" t="n"/>
+      <c r="C42" s="40" t="n"/>
+      <c r="D42" s="40" t="n"/>
+      <c r="E42" s="40" t="n"/>
+      <c r="F42" s="40" t="n"/>
+      <c r="G42" s="40" t="n"/>
+      <c r="H42" s="40" t="n"/>
+      <c r="I42" s="40" t="n"/>
+      <c r="J42" s="40" t="n"/>
+      <c r="K42" s="40" t="n"/>
+      <c r="L42" s="41" t="n"/>
+    </row>
+    <row r="43" ht="13" customHeight="1">
+      <c r="A43" s="17" t="inlineStr">
         <is>
           <t>•  Mahal listesi, mimari projenin ekinde sunulmak üzere hazırlanmıştır; mahal kodları mimari plandaki blok ve hacim adlarıyla eşleşir.</t>
         </is>
       </c>
     </row>
-    <row r="38" ht="13" customHeight="1">
-      <c r="A38" s="17" t="inlineStr">
+    <row r="44" ht="13" customHeight="1">
+      <c r="A44" s="17" t="inlineStr">
         <is>
           <t>•  Listede kullanılan poz numaraları metraj cetveli ve keşif özetiyle birebir aynıdır.</t>
         </is>
       </c>
     </row>
-    <row r="39" ht="13" customHeight="1">
-      <c r="A39" s="17" t="inlineStr">
+    <row r="45" ht="13" customHeight="1">
+      <c r="A45" s="17" t="inlineStr">
         <is>
           <t>•  Kümes A ve B blok birebir özdeş olduğundan tek mahal sütununda gösterilmiştir.</t>
         </is>
       </c>
     </row>
-    <row r="40" ht="22" customHeight="1">
-      <c r="A40" s="17" t="inlineStr">
+    <row r="46" ht="22" customHeight="1">
+      <c r="A46" s="17" t="inlineStr">
         <is>
           <t>•  Listedeki pozların tamamı birim fiyat kitaplarındandır: 15.xxx ÇŞB 2026 birim fiyat kitabı, TKDK-xxxx ise TKDK 17.02.2026 Özel Poz Tablosu pozudur.</t>
         </is>
       </c>
     </row>
-    <row r="41" ht="22" customHeight="1">
-      <c r="A41" s="17" t="inlineStr">
+    <row r="47" ht="22" customHeight="1">
+      <c r="A47" s="17" t="inlineStr">
+        <is>
+          <t>•  Sıhhi tesisat kalemlerinin kitap pozu yoktur ve keşif özetinde yer almazlar: miktarları onaylı sıhhi tesisat projesinden, bedelleri piyasa araştırmasından gelir ve 36 numaralı proforma ile beyan edilir. Poz sütununda “—” işareti bunu gösterir.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="22" customHeight="1">
+      <c r="A48" s="17" t="inlineStr">
         <is>
           <t>•  Gübre çukuru, ölü atma çukuru ve depoların iç yüzeyleri kaplamasız brüt betonarmedir; su yalıtımı bu hesabın kapsamı dışında bırakılmıştır. Foseptik betonarme değildir: kazı ve grobeton oturma yatağı üzerine yerleştirilen prefabrik polietilen sızdırmaz tanktır.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="16">
-    <mergeCell ref="A38:L38"/>
+  <mergeCells count="18">
     <mergeCell ref="A2:L2"/>
+    <mergeCell ref="A35:A40"/>
+    <mergeCell ref="A42:L42"/>
     <mergeCell ref="A22:A23"/>
-    <mergeCell ref="A41:L41"/>
+    <mergeCell ref="A43:L43"/>
     <mergeCell ref="A24:A27"/>
+    <mergeCell ref="A47:L47"/>
     <mergeCell ref="A1:L1"/>
     <mergeCell ref="A28:A30"/>
-    <mergeCell ref="A37:L37"/>
-    <mergeCell ref="A36:L36"/>
+    <mergeCell ref="A45:L45"/>
+    <mergeCell ref="A46:L46"/>
     <mergeCell ref="A11:A13"/>
-    <mergeCell ref="A40:L40"/>
+    <mergeCell ref="A44:L44"/>
     <mergeCell ref="A14:A21"/>
     <mergeCell ref="A31:A33"/>
     <mergeCell ref="A3:L3"/>
-    <mergeCell ref="A39:L39"/>
+    <mergeCell ref="A48:L48"/>
     <mergeCell ref="A6:A10"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/belgeler/05_MAHAL_LISTESI.xlsx
+++ b/belgeler/05_MAHAL_LISTESI.xlsx
@@ -1918,7 +1918,7 @@
     <row r="47" ht="22" customHeight="1">
       <c r="A47" s="17" t="inlineStr">
         <is>
-          <t>•  Sıhhi tesisat kalemlerinin kitap pozu yoktur ve keşif özetinde yer almazlar: miktarları onaylı sıhhi tesisat projesinden, bedelleri piyasa araştırmasından gelir ve 36 numaralı proforma ile beyan edilir. Poz sütununda “—” işareti bunu gösterir.</t>
+          <t>•  Sıhhi tesisat kalemlerinin kitap pozu yoktur ve keşif özetinde yer almazlar: miktarları onaylı sıhhi tesisat projesinden (39) gelir. Poz sütununda “—” işareti bunu gösterir.</t>
         </is>
       </c>
     </row>
